--- a/dist.orig/core_config.xlsx
+++ b/dist.orig/core_config.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="8"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="Repo" sheetId="1" state="visible" r:id="rId2"/>
@@ -21,6 +21,9 @@
     <sheet name="Alert" sheetId="13" state="visible" r:id="rId14"/>
     <sheet name="UserDefinedList" sheetId="14" state="visible" r:id="rId15"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">Alert!$A$1:$BF$109</definedName>
+  </definedNames>
   <calcPr iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
@@ -8452,8 +8455,9 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.25"/>
   <cols>
+    <col bestFit="1" min="1" max="1" width="84.57421875"/>
     <col customWidth="1" min="3" max="3" width="72.28515625"/>
   </cols>
   <sheetData>
@@ -8633,7 +8637,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="2" ht="15.199999999999999" customHeight="1">
+    <row r="2" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A2" t="s">
         <v>481</v>
       </c>
@@ -8757,7 +8761,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" ht="15.199999999999999" customHeight="1">
+    <row r="3" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A3" t="s">
         <v>500</v>
       </c>
@@ -8869,7 +8873,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" ht="15.199999999999999" customHeight="1">
+    <row r="4" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A4" t="s">
         <v>513</v>
       </c>
@@ -8987,7 +8991,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" ht="15.199999999999999" customHeight="1">
+    <row r="5" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A5" t="s">
         <v>513</v>
       </c>
@@ -9105,7 +9109,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" ht="15.199999999999999" customHeight="1">
+    <row r="6" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A6" t="s">
         <v>513</v>
       </c>
@@ -9223,7 +9227,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" ht="15.199999999999999" customHeight="1">
+    <row r="7" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A7" t="s">
         <v>526</v>
       </c>
@@ -9341,7 +9345,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" ht="15.199999999999999" customHeight="1">
+    <row r="8" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A8" t="s">
         <v>533</v>
       </c>
@@ -9575,10 +9579,10 @@
         <v>557</v>
       </c>
       <c r="BD9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" ht="15.199999999999999" customHeight="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A10" t="s">
         <v>558</v>
       </c>
@@ -9700,7 +9704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" ht="15.199999999999999" customHeight="1">
+    <row r="11" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A11" t="s">
         <v>566</v>
       </c>
@@ -9831,7 +9835,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="12" ht="15.199999999999999" customHeight="1">
+    <row r="12" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A12" t="s">
         <v>576</v>
       </c>
@@ -9962,7 +9966,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="13" ht="15.199999999999999" customHeight="1">
+    <row r="13" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A13" t="s">
         <v>585</v>
       </c>
@@ -10093,7 +10097,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="14" ht="15.199999999999999" customHeight="1">
+    <row r="14" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A14" t="s">
         <v>593</v>
       </c>
@@ -10218,7 +10222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" ht="15.199999999999999" customHeight="1">
+    <row r="15" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A15" t="s">
         <v>602</v>
       </c>
@@ -10349,7 +10353,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="16" ht="15.199999999999999" customHeight="1">
+    <row r="16" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A16" t="s">
         <v>606</v>
       </c>
@@ -10480,7 +10484,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="17" ht="15.199999999999999" customHeight="1">
+    <row r="17" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A17" t="s">
         <v>610</v>
       </c>
@@ -10611,7 +10615,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="18" ht="15.199999999999999" customHeight="1">
+    <row r="18" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A18" t="s">
         <v>614</v>
       </c>
@@ -10736,7 +10740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" ht="15.199999999999999" customHeight="1">
+    <row r="19" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A19" t="s">
         <v>618</v>
       </c>
@@ -10861,7 +10865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" ht="15.199999999999999" customHeight="1">
+    <row r="20" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A20" t="s">
         <v>627</v>
       </c>
@@ -10998,7 +11002,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="21" ht="15.199999999999999" customHeight="1">
+    <row r="21" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A21" t="s">
         <v>639</v>
       </c>
@@ -11135,7 +11139,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="22" ht="15.199999999999999" customHeight="1">
+    <row r="22" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A22" t="s">
         <v>649</v>
       </c>
@@ -11263,7 +11267,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="23" ht="15.199999999999999" customHeight="1">
+    <row r="23" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A23" t="s">
         <v>659</v>
       </c>
@@ -11391,7 +11395,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="24" ht="15.199999999999999" customHeight="1">
+    <row r="24" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A24" t="s">
         <v>666</v>
       </c>
@@ -11519,7 +11523,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="25" ht="15.199999999999999" customHeight="1">
+    <row r="25" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A25" t="s">
         <v>673</v>
       </c>
@@ -11653,7 +11657,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="26" ht="15.199999999999999" customHeight="1">
+    <row r="26" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A26" t="s">
         <v>681</v>
       </c>
@@ -11781,7 +11785,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="27" ht="15.199999999999999" customHeight="1">
+    <row r="27" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A27" t="s">
         <v>690</v>
       </c>
@@ -11909,7 +11913,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="28" ht="15.199999999999999" customHeight="1">
+    <row r="28" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A28" t="s">
         <v>697</v>
       </c>
@@ -12040,7 +12044,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="29" ht="15.199999999999999" customHeight="1">
+    <row r="29" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A29" t="s">
         <v>706</v>
       </c>
@@ -12162,7 +12166,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="30" ht="15.199999999999999" customHeight="1">
+    <row r="30" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A30" t="s">
         <v>716</v>
       </c>
@@ -12293,7 +12297,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" ht="15.199999999999999" customHeight="1">
+    <row r="31" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A31" t="s">
         <v>724</v>
       </c>
@@ -12418,7 +12422,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="32" ht="15.199999999999999" customHeight="1">
+    <row r="32" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A32" t="s">
         <v>731</v>
       </c>
@@ -12527,7 +12531,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="33" ht="15.199999999999999" customHeight="1">
+    <row r="33" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A33" t="s">
         <v>739</v>
       </c>
@@ -12664,7 +12668,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="34" ht="15.199999999999999" customHeight="1">
+    <row r="34" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A34" t="s">
         <v>566</v>
       </c>
@@ -12795,7 +12799,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="35" ht="15.199999999999999" customHeight="1">
+    <row r="35" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A35" t="s">
         <v>576</v>
       </c>
@@ -12926,7 +12930,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="36" ht="15.199999999999999" customHeight="1">
+    <row r="36" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A36" t="s">
         <v>585</v>
       </c>
@@ -13057,7 +13061,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="37" ht="15.199999999999999" customHeight="1">
+    <row r="37" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A37" t="s">
         <v>593</v>
       </c>
@@ -13185,7 +13189,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="38" ht="15.199999999999999" customHeight="1">
+    <row r="38" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A38" t="s">
         <v>602</v>
       </c>
@@ -13316,7 +13320,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="39" ht="15.199999999999999" customHeight="1">
+    <row r="39" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A39" t="s">
         <v>606</v>
       </c>
@@ -13447,7 +13451,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="40" ht="15.199999999999999" customHeight="1">
+    <row r="40" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A40" t="s">
         <v>610</v>
       </c>
@@ -13578,7 +13582,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="41" ht="15.199999999999999" customHeight="1">
+    <row r="41" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A41" t="s">
         <v>614</v>
       </c>
@@ -13706,7 +13710,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="42" ht="15.199999999999999" customHeight="1">
+    <row r="42" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A42" t="s">
         <v>618</v>
       </c>
@@ -13834,7 +13838,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="43" ht="15.199999999999999" customHeight="1">
+    <row r="43" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A43" t="s">
         <v>785</v>
       </c>
@@ -13968,7 +13972,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="44" ht="15.199999999999999" customHeight="1">
+    <row r="44" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A44" t="s">
         <v>793</v>
       </c>
@@ -14102,7 +14106,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="45" ht="15.199999999999999" customHeight="1">
+    <row r="45" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A45" t="s">
         <v>649</v>
       </c>
@@ -14230,7 +14234,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="46" ht="15.199999999999999" customHeight="1">
+    <row r="46" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A46" t="s">
         <v>659</v>
       </c>
@@ -14358,7 +14362,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="47" ht="15.199999999999999" customHeight="1">
+    <row r="47" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A47" t="s">
         <v>666</v>
       </c>
@@ -14486,7 +14490,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="48" ht="15.199999999999999" customHeight="1">
+    <row r="48" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A48" t="s">
         <v>673</v>
       </c>
@@ -14620,7 +14624,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="49" ht="15.199999999999999" customHeight="1">
+    <row r="49" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A49" t="s">
         <v>810</v>
       </c>
@@ -14754,7 +14758,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="50" ht="15.199999999999999" customHeight="1">
+    <row r="50" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A50" t="s">
         <v>681</v>
       </c>
@@ -14882,7 +14886,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="51" ht="15.199999999999999" customHeight="1">
+    <row r="51" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A51" t="s">
         <v>690</v>
       </c>
@@ -15010,7 +15014,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="52" ht="15.199999999999999" customHeight="1">
+    <row r="52" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A52" t="s">
         <v>697</v>
       </c>
@@ -15144,7 +15148,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="53" ht="15.199999999999999" customHeight="1">
+    <row r="53" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A53" t="s">
         <v>827</v>
       </c>
@@ -15278,7 +15282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" ht="15.199999999999999" customHeight="1">
+    <row r="54" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A54" t="s">
         <v>835</v>
       </c>
@@ -15412,7 +15416,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55" ht="15.199999999999999" customHeight="1">
+    <row r="55" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A55" t="s">
         <v>841</v>
       </c>
@@ -15546,7 +15550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" ht="15.199999999999999" customHeight="1">
+    <row r="56" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A56" t="s">
         <v>853</v>
       </c>
@@ -15680,7 +15684,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" ht="15.199999999999999" customHeight="1">
+    <row r="57" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A57" t="s">
         <v>862</v>
       </c>
@@ -15805,7 +15809,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="58" ht="15.199999999999999" customHeight="1">
+    <row r="58" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A58" t="s">
         <v>869</v>
       </c>
@@ -15933,7 +15937,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" ht="15.199999999999999" customHeight="1">
+    <row r="59" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A59" t="s">
         <v>875</v>
       </c>
@@ -16058,7 +16062,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="60" ht="15.199999999999999" customHeight="1">
+    <row r="60" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A60" t="s">
         <v>883</v>
       </c>
@@ -16195,7 +16199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" ht="15.199999999999999" customHeight="1">
+    <row r="61" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A61" t="s">
         <v>827</v>
       </c>
@@ -16332,7 +16336,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" ht="15.199999999999999" customHeight="1">
+    <row r="62" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A62" t="s">
         <v>835</v>
       </c>
@@ -16469,7 +16473,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="63" ht="15.199999999999999" customHeight="1">
+    <row r="63" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A63" t="s">
         <v>853</v>
       </c>
@@ -16606,7 +16610,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64" ht="15.199999999999999" customHeight="1">
+    <row r="64" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A64" t="s">
         <v>898</v>
       </c>
@@ -16731,7 +16735,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="65" ht="15.199999999999999" customHeight="1">
+    <row r="65" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A65" t="s">
         <v>904</v>
       </c>
@@ -16856,7 +16860,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="66" ht="15.199999999999999" customHeight="1">
+    <row r="66" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A66" t="s">
         <v>912</v>
       </c>
@@ -16981,7 +16985,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="67" ht="15.199999999999999" customHeight="1">
+    <row r="67" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A67" t="s">
         <v>920</v>
       </c>
@@ -17109,7 +17113,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="68" ht="15.199999999999999" customHeight="1">
+    <row r="68" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A68" t="s">
         <v>929</v>
       </c>
@@ -17237,7 +17241,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="69" ht="15.199999999999999" customHeight="1">
+    <row r="69" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A69" t="s">
         <v>936</v>
       </c>
@@ -17365,7 +17369,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="70" ht="15.199999999999999" customHeight="1">
+    <row r="70" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A70" t="s">
         <v>942</v>
       </c>
@@ -17493,7 +17497,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="71" ht="15.199999999999999" customHeight="1">
+    <row r="71" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A71" t="s">
         <v>946</v>
       </c>
@@ -17621,7 +17625,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="72" ht="15.199999999999999" customHeight="1">
+    <row r="72" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A72" t="s">
         <v>949</v>
       </c>
@@ -17749,7 +17753,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="73" ht="15.199999999999999" customHeight="1">
+    <row r="73" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A73" t="s">
         <v>952</v>
       </c>
@@ -17880,7 +17884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" ht="15.199999999999999" customHeight="1">
+    <row r="74" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A74" t="s">
         <v>959</v>
       </c>
@@ -18011,7 +18015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" ht="15.199999999999999" customHeight="1">
+    <row r="75" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A75" t="s">
         <v>966</v>
       </c>
@@ -18142,7 +18146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" ht="15.199999999999999" customHeight="1">
+    <row r="76" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A76" t="s">
         <v>973</v>
       </c>
@@ -18267,7 +18271,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="77" ht="15.199999999999999" customHeight="1">
+    <row r="77" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A77" t="s">
         <v>980</v>
       </c>
@@ -18392,7 +18396,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="78" ht="15.199999999999999" customHeight="1">
+    <row r="78" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A78" t="s">
         <v>986</v>
       </c>
@@ -18526,7 +18530,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="79" ht="15.199999999999999" customHeight="1">
+    <row r="79" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A79" t="s">
         <v>999</v>
       </c>
@@ -18660,7 +18664,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="80" ht="15.199999999999999" customHeight="1">
+    <row r="80" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A80" t="s">
         <v>1010</v>
       </c>
@@ -18794,7 +18798,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="81" ht="15.199999999999999" customHeight="1">
+    <row r="81" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A81" t="s">
         <v>1018</v>
       </c>
@@ -18931,7 +18935,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="82" ht="15.199999999999999" customHeight="1">
+    <row r="82" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A82" t="s">
         <v>1026</v>
       </c>
@@ -19068,7 +19072,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="83" ht="15.199999999999999" customHeight="1">
+    <row r="83" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A83" t="s">
         <v>1033</v>
       </c>
@@ -19193,7 +19197,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="84" ht="15.199999999999999" customHeight="1">
+    <row r="84" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A84" t="s">
         <v>1040</v>
       </c>
@@ -19321,7 +19325,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="85" ht="15.199999999999999" customHeight="1">
+    <row r="85" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A85" t="s">
         <v>1049</v>
       </c>
@@ -19455,7 +19459,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="86" ht="15.199999999999999" customHeight="1">
+    <row r="86" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A86" t="s">
         <v>1056</v>
       </c>
@@ -19589,7 +19593,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="87" ht="15.199999999999999" customHeight="1">
+    <row r="87" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A87" t="s">
         <v>1063</v>
       </c>
@@ -19717,7 +19721,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="88" ht="15.199999999999999" customHeight="1">
+    <row r="88" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A88" t="s">
         <v>1072</v>
       </c>
@@ -19854,7 +19858,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="89" ht="15.199999999999999" customHeight="1">
+    <row r="89" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A89" t="s">
         <v>1084</v>
       </c>
@@ -19991,7 +19995,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="90" ht="15.199999999999999" customHeight="1">
+    <row r="90" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A90" t="s">
         <v>1093</v>
       </c>
@@ -20128,7 +20132,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="91" ht="15.199999999999999" customHeight="1">
+    <row r="91" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A91" t="s">
         <v>1101</v>
       </c>
@@ -20253,7 +20257,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="92" ht="15.199999999999999" customHeight="1">
+    <row r="92" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A92" t="s">
         <v>1108</v>
       </c>
@@ -20390,7 +20394,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="93" ht="15.199999999999999" customHeight="1">
+    <row r="93" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A93" t="s">
         <v>1119</v>
       </c>
@@ -20521,7 +20525,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="94" ht="15.199999999999999" customHeight="1">
+    <row r="94" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A94" t="s">
         <v>1130</v>
       </c>
@@ -20658,7 +20662,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="95" ht="15.199999999999999" customHeight="1">
+    <row r="95" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A95" t="s">
         <v>1139</v>
       </c>
@@ -20795,7 +20799,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="96" ht="15.199999999999999" customHeight="1">
+    <row r="96" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A96" t="s">
         <v>1148</v>
       </c>
@@ -20932,7 +20936,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="97" ht="15.199999999999999" customHeight="1">
+    <row r="97" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A97" t="s">
         <v>1158</v>
       </c>
@@ -21069,7 +21073,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="98" ht="15.199999999999999" customHeight="1">
+    <row r="98" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A98" t="s">
         <v>1168</v>
       </c>
@@ -21206,7 +21210,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="99" ht="15.199999999999999" customHeight="1">
+    <row r="99" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A99" t="s">
         <v>1182</v>
       </c>
@@ -21343,7 +21347,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="100" ht="15.199999999999999" customHeight="1">
+    <row r="100" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A100" t="s">
         <v>1193</v>
       </c>
@@ -21480,7 +21484,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="101" ht="15.199999999999999" customHeight="1">
+    <row r="101" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A101" t="s">
         <v>1202</v>
       </c>
@@ -21617,7 +21621,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="102" ht="15.199999999999999" customHeight="1">
+    <row r="102" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A102" t="s">
         <v>1212</v>
       </c>
@@ -21754,7 +21758,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="103" ht="15.199999999999999" customHeight="1">
+    <row r="103" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A103" t="s">
         <v>1225</v>
       </c>
@@ -21891,7 +21895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" ht="15.199999999999999" customHeight="1">
+    <row r="104" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A104" t="s">
         <v>1237</v>
       </c>
@@ -22028,7 +22032,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="105" ht="15.199999999999999" customHeight="1">
+    <row r="105" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A105" t="s">
         <v>1250</v>
       </c>
@@ -22162,7 +22166,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106" ht="15.199999999999999" customHeight="1">
+    <row r="106" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A106" t="s">
         <v>1259</v>
       </c>
@@ -22296,7 +22300,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" ht="15.199999999999999" customHeight="1">
+    <row r="107" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A107" t="s">
         <v>1268</v>
       </c>
@@ -22427,7 +22431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" ht="15.199999999999999" customHeight="1">
+    <row r="108" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A108" t="s">
         <v>1275</v>
       </c>
@@ -22558,7 +22562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" ht="15.199999999999999" customHeight="1">
+    <row r="109" ht="15.199999999999999" hidden="1" customHeight="1">
       <c r="A109" t="s">
         <v>1281</v>
       </c>
@@ -22693,6 +22697,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:BF109">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Erreur Paiement Mercanet Internet RSP"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.51181102362204689" footer="0.51181102362204689"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -33855,7 +33866,7 @@
         <v>215</v>
       </c>
       <c r="H2" t="b">
-        <f t="shared" ref="H2:H13" si="5">TRUE()</f>
+        <f t="shared" ref="H2:H15" si="5">TRUE()</f>
         <v>1</v>
       </c>
       <c r="I2" t="s">
@@ -34305,7 +34316,7 @@
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="I14" s="2" t="s">
@@ -34343,7 +34354,7 @@
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="I15" s="2" t="s">
@@ -34374,7 +34385,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.25"/>
   <cols>
     <col bestFit="1" customWidth="1" min="1" max="1" width="26"/>
     <col bestFit="1" customWidth="1" min="2" max="2" width="26.5703125"/>
